--- a/apps/web/public/importmallar/importmall-enheter.xlsx
+++ b/apps/web/public/importmallar/importmall-enheter.xlsx
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -122,6 +122,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -133,8 +134,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1" style="4"/>
+    <col min="2" max="2" width="14" customWidth="1" style="4"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
@@ -200,66 +201,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artikelnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Numret på en artikel som redan finns i artikelregistret.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RS-12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enhet</t>
+          <t xml:space="preserve">Artikelnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -269,19 +255,19 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Den alternativa enhetens kod, max 20 tecken. En okänd kod skapas i enhetsregistret. Samma enhet och artikel får bara förekomma en gång i filen.</t>
+          <t xml:space="preserve">Numret på en artikel som redan finns i artikelregistret.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">m</t>
+          <t xml:space="preserve">RS-12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omräkningsfaktor</t>
+          <t xml:space="preserve">Enhet</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -291,54 +277,76 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antal grundenheter per en alternativ enhet, större än 0, decimalkomma eller punkt — med grundenhet kg betyder 0,89 på raden m att en meter väger 0,89 kg. Lagras inverterat som alternativa enheter per grundenhet med sex decimaler. Faktor 1 markerar grundenhetsraden, som hoppas över (ska ha artikelns grundenhet, annars en varning).</t>
+          <t xml:space="preserve">Den alternativa enhetens kod, max 20 tecken. En okänd kod skapas i enhetsregistret. Samma enhet och artikel får bara förekomma en gång i filen.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,89</t>
+          <t xml:space="preserve">m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inköpsenhet</t>
+          <t xml:space="preserve">Omräkningsfaktor</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej. Ja gör enheten till artikelns inköpsenhet (förvalet på inköpsorderrader) — högst en per artikel i filen.</t>
+          <t xml:space="preserve">Antal grundenheter per en alternativ enhet, större än 0, decimalkomma eller punkt — med grundenhet kg betyder 0,89 på raden m att en meter väger 0,89 kg. Lagras inverterat som alternativa enheter per grundenhet med sex decimaler. Faktor 1 markerar grundenhetsraden, som hoppas över (ska ha artikelns grundenhet, annars en varning).</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">0,89</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inköpsenhet</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej. Ja gör enheten till artikelns inköpsenhet (förvalet på inköpsorderrader) — högst en per artikel i filen.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Försäljningsenhet</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej. Ja gör enheten till artikelns försäljningsenhet (förvalet på kundorderrader) — högst en per artikel i filen.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
